--- a/test_samples/DHL/sample2_ref.xlsx
+++ b/test_samples/DHL/sample2_ref.xlsx
@@ -516,7 +516,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>26.12.2024</t>
+          <t>26 Dec 2024</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>26.12.2024</t>
+          <t>26 Dec 2024</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>26.12.2024</t>
+          <t>26 Dec 2024</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -756,7 +756,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>26.12.2024</t>
+          <t>26 Dec 2024</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26.12.2024</t>
+          <t>26 Dec 2024</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -916,7 +916,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>26.12.2024</t>
+          <t>26 Dec 2024</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -996,7 +996,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>26.12.2024</t>
+          <t>26 Dec 2024</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1076,7 +1076,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>26.12.2024</t>
+          <t>26 Dec 2024</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1156,7 +1156,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>26.12.2024</t>
+          <t>26 Dec 2024</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1236,7 +1236,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>26.12.2024</t>
+          <t>26 Dec 2024</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1316,7 +1316,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26.12.2024</t>
+          <t>26 Dec 2024</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>26.12.2024</t>
+          <t>26 Dec 2024</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1476,7 +1476,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>27.12.2024</t>
+          <t>27 Dec 2024</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1556,7 +1556,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>27.12.2024</t>
+          <t>27 Dec 2024</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27.12.2024</t>
+          <t>27 Dec 2024</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1716,7 +1716,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>28.12.2024</t>
+          <t>28 Dec 2024</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1796,7 +1796,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>28.12.2024</t>
+          <t>28 Dec 2024</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1876,7 +1876,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>28.12.2024</t>
+          <t>28 Dec 2024</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1956,7 +1956,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>02.01.2025</t>
+          <t>02 Jan 2025</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2036,7 +2036,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>02.01.2025</t>
+          <t>02 Jan 2025</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07.01.2025</t>
+          <t>07 Jan 2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>02.01.2025</t>
+          <t>02 Jan 2025</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
